--- a/hiv_curation.xlsx
+++ b/hiv_curation.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="680" windowWidth="16840" windowHeight="17120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3280" yWindow="680" windowWidth="16840" windowHeight="17120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -121,6 +121,19 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF12161C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
@@ -131,7 +144,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -192,6 +205,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7A3F6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007A3F6E"/>
       </patternFill>
     </fill>
@@ -201,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -252,6 +275,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFDFE3E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDFE3E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDFE3E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDFE3E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="00DFE3E8"/>
       </left>
       <right style="thin">
@@ -269,7 +307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,6 +351,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -323,16 +371,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,43 +635,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD48"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="22" min="1" max="1"/>
-    <col width="13" customWidth="1" style="22" min="2" max="2"/>
-    <col width="40" customWidth="1" style="22" min="3" max="3"/>
-    <col width="12" customWidth="1" style="22" min="4" max="6"/>
-    <col width="30" customWidth="1" style="22" min="7" max="7"/>
-    <col width="16" customWidth="1" style="22" min="8" max="8"/>
-    <col width="5" customWidth="1" style="22" min="9" max="22"/>
-    <col width="17" customWidth="1" style="22" min="23" max="23"/>
-    <col width="9" customWidth="1" style="22" min="24" max="24"/>
-    <col width="10" customWidth="1" style="22" min="25" max="25"/>
-    <col width="26" customWidth="1" style="22" min="26" max="26"/>
-    <col width="9" customWidth="1" style="22" min="27" max="27"/>
-    <col width="34" customWidth="1" style="22" min="28" max="28"/>
-    <col width="8" customWidth="1" style="22" min="30" max="30"/>
+    <col width="6" customWidth="1" style="26" min="1" max="1"/>
+    <col width="13" customWidth="1" style="26" min="2" max="2"/>
+    <col width="40" customWidth="1" style="26" min="3" max="3"/>
+    <col width="12" customWidth="1" style="26" min="4" max="6"/>
+    <col width="30" customWidth="1" style="26" min="7" max="7"/>
+    <col width="16" customWidth="1" style="26" min="8" max="8"/>
+    <col width="5" customWidth="1" style="26" min="9" max="22"/>
+    <col width="17" customWidth="1" style="26" min="23" max="23"/>
+    <col width="9" customWidth="1" style="26" min="24" max="24"/>
+    <col width="10" customWidth="1" style="26" min="25" max="25"/>
+    <col width="26" customWidth="1" style="26" min="26" max="26"/>
+    <col width="9" customWidth="1" style="26" min="27" max="27"/>
+    <col width="34" customWidth="1" style="26" min="28" max="28"/>
+    <col width="8" customWidth="1" style="26" min="30" max="30"/>
+    <col width="26" customWidth="1" style="26" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="22">
-      <c r="I1" s="23" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="26">
+      <c r="I1" s="27" t="inlineStr">
         <is>
           <t>ROUTE  (mark x)</t>
         </is>
       </c>
-      <c r="O1" s="24" t="inlineStr">
+      <c r="O1" s="28" t="inlineStr">
         <is>
           <t>DOSING INTERVAL  (mark x)</t>
         </is>
       </c>
-      <c r="AA1" s="21" t="inlineStr">
+      <c r="AA1" s="25" t="inlineStr">
         <is>
           <t>EXCLUDE FROM DASHBOARD</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="22">
+    <row r="2" ht="33.75" customHeight="1" s="26">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -770,18 +813,23 @@
           <t>exclude_reason</t>
         </is>
       </c>
-      <c r="AC2" s="25" t="inlineStr">
+      <c r="AC2" s="21" t="inlineStr">
         <is>
           <t>link in LAPaL</t>
         </is>
       </c>
-      <c r="AD2" s="27" t="inlineStr">
+      <c r="AD2" s="23" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="22">
+      <c r="AE2" s="29" t="inlineStr">
+        <is>
+          <t>class_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="26">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>f001</t>
@@ -855,9 +903,14 @@
           <t>https://lapal.ch/formulations/lenacapavir-6-monthly</t>
         </is>
       </c>
-      <c r="AD3" s="28" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="22">
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="26">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>f002</t>
@@ -939,9 +992,14 @@
           <t>https://lapal.ch/formulations/cab-la-cabotegravir-2-monthly</t>
         </is>
       </c>
-      <c r="AD4" s="28" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="22">
+      <c r="AD4" s="24" t="n"/>
+      <c r="AE4" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="26">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>f003</t>
@@ -1019,9 +1077,14 @@
           <t>https://lapal.ch/formulations/rilpivirine-2-monthly</t>
         </is>
       </c>
-      <c r="AD5" s="28" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="22">
+      <c r="AD5" s="24" t="n"/>
+      <c r="AE5" s="30" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="26">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>f004</t>
@@ -1107,9 +1170,14 @@
           <t>https://lapal.ch/formulations/cabotegravir-rilpivirine</t>
         </is>
       </c>
-      <c r="AD6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="22">
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="30" t="inlineStr">
+        <is>
+          <t>INSTI + NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="26">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>f005</t>
@@ -1191,9 +1259,14 @@
           <t>https://lapal.ch/formulations/lotivibart-n6ls-vh3810109-mab</t>
         </is>
       </c>
-      <c r="AD7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="22">
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="26">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>f006</t>
@@ -1275,9 +1348,14 @@
           <t>https://lapal.ch/formulations/teropavimab-zinlirvimab</t>
         </is>
       </c>
-      <c r="AD8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="22">
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="26">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>f007</t>
@@ -1363,9 +1441,14 @@
           <t>https://lapal.ch/formulations/tenofovir-lamivudine-dolutegravir-tld-long-acting-injectable-lai-tld-lai</t>
         </is>
       </c>
-      <c r="AD9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="22">
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="30" t="inlineStr">
+        <is>
+          <t>INSTI + NRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="26">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>f008</t>
@@ -1451,9 +1534,14 @@
           <t>https://lapal.ch/formulations/ibalizumab</t>
         </is>
       </c>
-      <c r="AD10" s="28" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="22">
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="26">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>f009</t>
@@ -1530,14 +1618,19 @@
       <c r="Z11" s="5" t="n"/>
       <c r="AA11" s="19" t="n"/>
       <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="26" t="inlineStr">
+      <c r="AC11" s="22" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/budigalimab</t>
         </is>
       </c>
-      <c r="AD11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="22">
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="26">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>f010</t>
@@ -1623,9 +1716,14 @@
           <t>https://lapal.ch/formulations/vrc07-523ls-mab</t>
         </is>
       </c>
-      <c r="AD12" s="28" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="22">
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="26">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>f011</t>
@@ -1711,9 +1809,14 @@
           <t>https://lapal.ch/formulations/bictegravir-la</t>
         </is>
       </c>
-      <c r="AD13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="22">
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="26">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>f012</t>
@@ -1803,9 +1906,14 @@
           <t>https://lapal.ch/formulations/cabotegravir-lenacapavir</t>
         </is>
       </c>
-      <c r="AD14" s="28" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="22">
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="26">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>f013</t>
@@ -1883,9 +1991,14 @@
           <t>https://lapal.ch/formulations/mk-8591d-islatravir-and-lenacapavir</t>
         </is>
       </c>
-      <c r="AD15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="22">
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + NRTTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="26">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>f014</t>
@@ -1963,9 +2076,14 @@
           <t>https://lapal.ch/formulations/cabotegravir-4-monthly-q4m</t>
         </is>
       </c>
-      <c r="AD16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="22">
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="26">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>f015</t>
@@ -2047,9 +2165,14 @@
           <t>https://lapal.ch/formulations/rilpivirine-prodrug-nanoformulation-nm3rpv</t>
         </is>
       </c>
-      <c r="AD17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="22">
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="30" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="26">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>f016</t>
@@ -2127,9 +2250,14 @@
           <t>https://lapal.ch/formulations/bictegravir-la</t>
         </is>
       </c>
-      <c r="AD18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="22">
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="30" t="inlineStr">
+        <is>
+          <t>NRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="26">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>f017</t>
@@ -2207,9 +2335,14 @@
           <t>https://lapal.ch/formulations/lenacapavir-once-yearly</t>
         </is>
       </c>
-      <c r="AD19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="22">
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="26">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>f018</t>
@@ -2287,9 +2420,14 @@
           <t>https://lapal.ch/formulations/cabotegravir-ph20</t>
         </is>
       </c>
-      <c r="AD20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="22">
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="26">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>f019</t>
@@ -2383,9 +2521,14 @@
           <t>https://lapal.ch/formulations/vrc01-mab</t>
         </is>
       </c>
-      <c r="AD21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="22">
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="26">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>f020</t>
@@ -2463,9 +2606,14 @@
           <t>https://lapal.ch/formulations/mk-8591b-islatravir-ulonivirine</t>
         </is>
       </c>
-      <c r="AD22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="22">
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="30" t="inlineStr">
+        <is>
+          <t>NRTTI + NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="26">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>f021</t>
@@ -2547,9 +2695,14 @@
           <t>https://lapal.ch/formulations/vh-280-vh-4004280</t>
         </is>
       </c>
-      <c r="AD23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="22">
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="26">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>f022</t>
@@ -2627,9 +2780,14 @@
           <t>https://lapal.ch/formulations/pgt-121-mab</t>
         </is>
       </c>
-      <c r="AD24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="22">
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="26">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>f023</t>
@@ -2711,9 +2869,14 @@
           <t>https://lapal.ch/formulations/pgdm1400-mab</t>
         </is>
       </c>
-      <c r="AD25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="22">
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>f024</t>
@@ -2795,9 +2958,14 @@
           <t>https://lapal.ch/formulations/lopinavir-ritonavir-and-tenofovir-lrt-tlc-art-101</t>
         </is>
       </c>
-      <c r="AD26" s="28" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="22">
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="30" t="inlineStr">
+        <is>
+          <t>NRTI + PI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="26">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>f025</t>
@@ -2879,9 +3047,14 @@
           <t>https://lapal.ch/formulations/ultra-long-acting-dimeric-bictegravir-prodrug</t>
         </is>
       </c>
-      <c r="AD27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="22">
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="26">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>f026</t>
@@ -2963,9 +3136,14 @@
           <t>https://lapal.ch/formulations/lenacapavir-teropavimab-zinlirvimab</t>
         </is>
       </c>
-      <c r="AD28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="22">
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="26">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>f027</t>
@@ -3051,9 +3229,14 @@
           <t>https://lapal.ch/formulations/pgt121414ls-vrc07-523ls-mab</t>
         </is>
       </c>
-      <c r="AD29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="22">
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="30" t="inlineStr">
+        <is>
+          <t>mAb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="26">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>f028</t>
@@ -3131,9 +3314,14 @@
           <t>https://lapal.ch/formulations/lepetegravir-lenacapavir-pacfosacil-gs-1720gs-4182</t>
         </is>
       </c>
-      <c r="AD30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="22">
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="26">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>f029</t>
@@ -3211,9 +3399,14 @@
           <t>https://lapal.ch/formulations/bictegravir-plga-nanoformulation</t>
         </is>
       </c>
-      <c r="AD31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="22">
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="26">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>c030</t>
@@ -3291,9 +3484,14 @@
           <t>https://lapal.ch/compounds/ulonivirine-mk-8507</t>
         </is>
       </c>
-      <c r="AD32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="22">
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="30" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="26">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>c032</t>
@@ -3371,9 +3569,14 @@
           <t>https://lapal.ch/compounds/lepetegravir-gs-1720</t>
         </is>
       </c>
-      <c r="AD33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="22">
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="26">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>c033</t>
@@ -3463,9 +3666,14 @@
           <t>https://lapal.ch/compounds/cabotegravir</t>
         </is>
       </c>
-      <c r="AD34" s="28" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="22">
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="26">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>c034</t>
@@ -3547,9 +3755,14 @@
           <t>https://lapal.ch/compounds/islatravir-isl</t>
         </is>
       </c>
-      <c r="AD35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="22">
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="30" t="inlineStr">
+        <is>
+          <t>NRTTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="26">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>c035</t>
@@ -3627,9 +3840,14 @@
           <t>https://lapal.ch/technology/dapivirine-monthly-vaginal-ring</t>
         </is>
       </c>
-      <c r="AD36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="22">
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="30" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="26">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>c037</t>
@@ -3719,9 +3937,14 @@
           <t>https://lapal.ch/compounds/vh-310-vh-4367310</t>
         </is>
       </c>
-      <c r="AD37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="22">
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="26">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>c038</t>
@@ -3799,9 +4022,14 @@
           <t>https://lapal.ch/compounds/lenacapavir-pacfosacil-gs-4182</t>
         </is>
       </c>
-      <c r="AD38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="22">
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="26">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>c039</t>
@@ -3891,9 +4119,14 @@
           <t>https://lapal.ch/compounds/lenacapavir-len</t>
         </is>
       </c>
-      <c r="AD39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="22">
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="26">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>c040</t>
@@ -3979,9 +4212,14 @@
           <t>https://lapal.ch/compounds/gs-3242</t>
         </is>
       </c>
-      <c r="AD40" s="28" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="22">
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="26">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>c041</t>
@@ -4075,9 +4313,14 @@
           <t>https://lapal.ch/compounds/vh-499-vh-4011499</t>
         </is>
       </c>
-      <c r="AD41" s="28" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="22">
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="26">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>c042</t>
@@ -4171,9 +4414,14 @@
           <t>https://lapal.ch/compounds/vh-184-vh-4524184</t>
         </is>
       </c>
-      <c r="AD42" s="28" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="22">
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="30" t="inlineStr">
+        <is>
+          <t>INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="26">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>c043</t>
@@ -4251,9 +4499,14 @@
           <t>https://lapal.ch/compounds/depulfavirine-nanosphere-lai</t>
         </is>
       </c>
-      <c r="AD43" s="28" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="22">
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="30" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="26">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>c044</t>
@@ -4331,9 +4584,14 @@
           <t>https://lapal.ch/compounds/alimatravir-mk-8527</t>
         </is>
       </c>
-      <c r="AD44" s="28" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="22">
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="30" t="inlineStr">
+        <is>
+          <t>NRTTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="26">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>c045</t>
@@ -4415,11 +4673,16 @@
           <t>https://lapal.ch/compounds/gs-3107</t>
         </is>
       </c>
-      <c r="AD45" s="28" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="30" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
     </row>
     <row r="46"/>
     <row r="47"/>
-    <row r="48" ht="15" customHeight="1" s="22">
+    <row r="48" ht="15" customHeight="1" s="26">
       <c r="Z48" s="9" t="inlineStr">
         <is>
           <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
@@ -4432,7 +4695,7 @@
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:V1"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="B3:B45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose formulations or compounds" prompt="Choose formulations or compounds" type="list">
       <formula1>"formulations,compounds"</formula1>
       <formula2>0</formula2>
@@ -4460,6 +4723,9 @@
     <dataValidation sqref="AA3:AA48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Leave blank to show the entry. Type x to hide it from the dashboard." prompt="Leave blank to show the entry. Type x to hide it from the dashboard." type="list">
       <formula1>"x"</formula1>
     </dataValidation>
+    <dataValidation sqref="AE3:AE48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a class, or a combination for a multi-class product." prompt="Pick a class, or a combination for a multi-class product." type="list">
+      <formula1>"Capsid inhibitor,INSTI,NNRTI,NRTI,NRTTI,mAb,PI,Fusion inhibitor,Capsid inhibitor + INSTI,Capsid inhibitor + NRTTI,Capsid inhibitor + mAb,INSTI + NNRTI,INSTI + NRTI,NRTI + PI,NRTTI + NNRTI"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC11" r:id="rId1"/>
@@ -4478,11 +4744,11 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="22" min="1" max="1"/>
-    <col width="88" customWidth="1" style="22" min="2" max="2"/>
+    <col width="26" customWidth="1" style="26" min="1" max="1"/>
+    <col width="88" customWidth="1" style="26" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.25" customHeight="1" s="22">
+    <row r="1" ht="16.25" customHeight="1" s="26">
       <c r="A1" s="10" t="inlineStr">
         <is>
           <t>LAPaL long-acting HIV</t>
@@ -4494,11 +4760,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="22">
+    <row r="2" ht="15" customHeight="1" s="26">
       <c r="A2" s="12" t="n"/>
       <c r="B2" s="13" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="22">
+    <row r="3" ht="15" customHeight="1" s="26">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
@@ -4506,7 +4772,7 @@
       </c>
       <c r="B3" s="15" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="22">
+    <row r="4" ht="15" customHeight="1" s="26">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>1. Edit the Entries tab</t>
@@ -4518,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="22">
+    <row r="5" ht="15" customHeight="1" s="26">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>2. Save the file</t>
@@ -4530,7 +4796,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="39" customHeight="1" s="22">
+    <row r="6" ht="39" customHeight="1" s="26">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>3. Run the build step</t>
@@ -4542,7 +4808,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="23.75" customHeight="1" s="22">
+    <row r="7" ht="23.75" customHeight="1" s="26">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>4. Refresh the dashboard</t>
@@ -4554,11 +4820,11 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="22">
+    <row r="8" ht="15" customHeight="1" s="26">
       <c r="A8" s="12" t="n"/>
       <c r="B8" s="13" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="22">
+    <row r="9" ht="15" customHeight="1" s="26">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>COLUMNS</t>
@@ -4566,7 +4832,7 @@
       </c>
       <c r="B9" s="15" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="22">
+    <row r="10" ht="15" customHeight="1" s="26">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>id</t>
@@ -4578,7 +4844,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="22">
+    <row r="11" ht="15" customHeight="1" s="26">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>band</t>
@@ -4590,7 +4856,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="22">
+    <row r="12" ht="15" customHeight="1" s="26">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>name</t>
@@ -4602,7 +4868,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="23.75" customHeight="1" s="22">
+    <row r="13" ht="23.75" customHeight="1" s="26">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>indication</t>
@@ -4614,7 +4880,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="22">
+    <row r="14" ht="15" customHeight="1" s="26">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>stage</t>
@@ -4626,7 +4892,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="22">
+    <row r="15" ht="15" customHeight="1" s="26">
       <c r="A15" s="12" t="inlineStr">
         <is>
           <t>highest_phase</t>
@@ -4638,7 +4904,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="22">
+    <row r="16" ht="15" customHeight="1" s="26">
       <c r="A16" s="12" t="inlineStr">
         <is>
           <t>developers</t>
@@ -4650,7 +4916,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="22">
+    <row r="17" ht="15" customHeight="1" s="26">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>drug_class</t>
@@ -4662,7 +4928,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="23.75" customHeight="1" s="22">
+    <row r="18" ht="23.75" customHeight="1" s="26">
       <c r="A18" s="12" t="inlineStr">
         <is>
           <t>ROUTE columns</t>
@@ -4674,7 +4940,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="23.75" customHeight="1" s="22">
+    <row r="19" ht="23.75" customHeight="1" s="26">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>INTERVAL columns</t>
@@ -4686,7 +4952,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="23.75" customHeight="1" s="22">
+    <row r="20" ht="23.75" customHeight="1" s="26">
       <c r="A20" s="12" t="inlineStr">
         <is>
           <t>frequency_source</t>
@@ -4698,7 +4964,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="22">
+    <row r="21" ht="15" customHeight="1" s="26">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>flag_no_trials</t>
@@ -4710,7 +4976,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="22">
+    <row r="22" ht="15" customHeight="1" s="26">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t>flag_no_reg_rows</t>
@@ -4722,7 +4988,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="22">
+    <row r="23" ht="15" customHeight="1" s="26">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>curator_notes</t>
@@ -4734,11 +5000,11 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="22">
+    <row r="24" ht="15" customHeight="1" s="26">
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="22">
+    <row r="25" ht="15" customHeight="1" s="26">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>AUTOMATIC FLAGS</t>
@@ -4750,7 +5016,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="22">
+    <row r="26" ht="15" customHeight="1" s="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>missing_frequency</t>
@@ -4762,7 +5028,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="23.75" customHeight="1" s="22">
+    <row r="27" ht="23.75" customHeight="1" s="26">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>conventional_approval_only</t>
@@ -4774,11 +5040,11 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="22">
+    <row r="28" ht="15" customHeight="1" s="26">
       <c r="A28" s="12" t="n"/>
       <c r="B28" s="13" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="22">
+    <row r="29" ht="15" customHeight="1" s="26">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>RULES THE BUILD STEP CHECKS</t>
@@ -4786,7 +5052,7 @@
       </c>
       <c r="B29" s="17" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="22">
+    <row r="30" ht="15" customHeight="1" s="26">
       <c r="A30" s="12" t="inlineStr">
         <is>
           <t>every row needs</t>
@@ -4798,7 +5064,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="22">
+    <row r="31" ht="15" customHeight="1" s="26">
       <c r="A31" s="12" t="inlineStr">
         <is>
           <t>controlled values</t>

--- a/hiv_curation.xlsx
+++ b/hiv_curation.xlsx
@@ -3,13 +3,15 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3280" yWindow="680" windowWidth="16840" windowHeight="17120" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20660" yWindow="1900" windowWidth="29080" windowHeight="21800" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Legend &amp; how to use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entries'!$A$2:$AE$2</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -57,13 +59,6 @@
       <b val="1"/>
       <color rgb="FF12161C"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF5A6472"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -134,14 +129,35 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="0012161C"/>
+      <family val="2"/>
+      <color rgb="FF12161C"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Manrope"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="15">
@@ -215,12 +231,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007A3F6E"/>
+        <fgColor rgb="FF7A3F6E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3E8F0"/>
+        <fgColor rgb="FFF3E8F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -290,24 +306,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DFE3E8"/>
+        <color rgb="FFDFE3E8"/>
       </left>
       <right style="thin">
-        <color rgb="00DFE3E8"/>
+        <color rgb="FFDFE3E8"/>
       </right>
       <top style="thin">
-        <color rgb="00DFE3E8"/>
+        <color rgb="FFDFE3E8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DFE3E8"/>
+        <color rgb="FFDFE3E8"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -328,40 +345,43 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -371,10 +391,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,44 +656,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="26" min="1" max="1"/>
-    <col width="13" customWidth="1" style="26" min="2" max="2"/>
-    <col width="40" customWidth="1" style="26" min="3" max="3"/>
-    <col width="12" customWidth="1" style="26" min="4" max="6"/>
-    <col width="30" customWidth="1" style="26" min="7" max="7"/>
-    <col width="16" customWidth="1" style="26" min="8" max="8"/>
-    <col width="5" customWidth="1" style="26" min="9" max="22"/>
-    <col width="17" customWidth="1" style="26" min="23" max="23"/>
-    <col width="9" customWidth="1" style="26" min="24" max="24"/>
-    <col width="10" customWidth="1" style="26" min="25" max="25"/>
-    <col width="26" customWidth="1" style="26" min="26" max="26"/>
-    <col width="9" customWidth="1" style="26" min="27" max="27"/>
-    <col width="34" customWidth="1" style="26" min="28" max="28"/>
-    <col width="8" customWidth="1" style="26" min="30" max="30"/>
-    <col width="26" customWidth="1" style="26" min="31" max="31"/>
+    <col width="6" customWidth="1" style="27" min="1" max="1"/>
+    <col width="13" customWidth="1" style="27" min="2" max="2"/>
+    <col width="55.83203125" customWidth="1" style="27" min="3" max="3"/>
+    <col width="12" customWidth="1" style="27" min="4" max="6"/>
+    <col width="30" customWidth="1" style="27" min="7" max="7"/>
+    <col width="21.1640625" customWidth="1" style="27" min="8" max="8"/>
+    <col width="13.33203125" customWidth="1" style="27" min="9" max="10"/>
+    <col width="5" customWidth="1" style="27" min="11" max="11"/>
+    <col width="8" customWidth="1" style="27" min="12" max="12"/>
+    <col width="5" customWidth="1" style="27" min="13" max="16"/>
+    <col width="7.6640625" customWidth="1" style="27" min="17" max="17"/>
+    <col width="8.5" customWidth="1" style="27" min="18" max="18"/>
+    <col width="9" customWidth="1" style="27" min="19" max="21"/>
+    <col width="7.33203125" customWidth="1" style="27" min="22" max="22"/>
+    <col width="17" customWidth="1" style="27" min="23" max="23"/>
+    <col width="9" customWidth="1" style="27" min="24" max="24"/>
+    <col width="10" customWidth="1" style="27" min="25" max="25"/>
+    <col width="11.33203125" customWidth="1" style="27" min="26" max="26"/>
+    <col width="9" customWidth="1" style="27" min="27" max="27"/>
+    <col width="34" customWidth="1" style="27" min="28" max="28"/>
+    <col width="17.1640625" customWidth="1" style="27" min="29" max="29"/>
+    <col width="22.33203125" customWidth="1" style="27" min="30" max="30"/>
+    <col width="26" customWidth="1" style="27" min="31" max="31"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="26">
-      <c r="I1" s="27" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="27">
+      <c r="I1" s="28" t="inlineStr">
         <is>
           <t>ROUTE  (mark x)</t>
         </is>
       </c>
-      <c r="O1" s="28" t="inlineStr">
+      <c r="O1" s="29" t="inlineStr">
         <is>
           <t>DOSING INTERVAL  (mark x)</t>
         </is>
       </c>
-      <c r="AA1" s="25" t="inlineStr">
+      <c r="AA1" s="26" t="inlineStr">
         <is>
           <t>EXCLUDE FROM DASHBOARD</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="26">
+    <row r="2" ht="33.75" customHeight="1" s="27">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -803,33 +832,33 @@
           <t>curator_notes</t>
         </is>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
+      <c r="AA2" s="17" t="inlineStr">
         <is>
           <t>exclude</t>
         </is>
       </c>
-      <c r="AB2" s="18" t="inlineStr">
+      <c r="AB2" s="17" t="inlineStr">
         <is>
           <t>exclude_reason</t>
         </is>
       </c>
-      <c r="AC2" s="21" t="inlineStr">
+      <c r="AC2" s="20" t="inlineStr">
         <is>
           <t>link in LAPaL</t>
         </is>
       </c>
-      <c r="AD2" s="23" t="inlineStr">
+      <c r="AD2" s="22" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="AE2" s="29" t="inlineStr">
+      <c r="AE2" s="24" t="inlineStr">
         <is>
           <t>class_group</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="26">
+    <row r="3" ht="15" customHeight="1" s="27">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>f001</t>
@@ -847,7 +876,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Prevention</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -855,13 +884,21 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Phase IV</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Gilead</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor</t>
+        </is>
+      </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
           <t>x</t>
@@ -896,21 +933,21 @@
       <c r="X3" s="5" t="n"/>
       <c r="Y3" s="5" t="n"/>
       <c r="Z3" s="5" t="n"/>
-      <c r="AA3" s="19" t="n"/>
-      <c r="AB3" s="20" t="n"/>
+      <c r="AA3" s="18" t="n"/>
+      <c r="AB3" s="19" t="n"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lenacapavir-6-monthly</t>
         </is>
       </c>
-      <c r="AD3" s="24" t="n"/>
-      <c r="AE3" s="30" t="inlineStr">
+      <c r="AD3" s="23" t="n"/>
+      <c r="AE3" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
+    <row r="4" ht="15" customHeight="1" s="27">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>f002</t>
@@ -928,7 +965,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Prevention</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -936,7 +973,11 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Phase IV</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
           <t>ViiV Healthcare</t>
@@ -944,7 +985,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -985,21 +1026,21 @@
       <c r="X4" s="5" t="n"/>
       <c r="Y4" s="5" t="n"/>
       <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="19" t="n"/>
-      <c r="AB4" s="20" t="n"/>
+      <c r="AA4" s="18" t="n"/>
+      <c r="AB4" s="19" t="n"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/cab-la-cabotegravir-2-monthly</t>
         </is>
       </c>
-      <c r="AD4" s="24" t="n"/>
-      <c r="AE4" s="30" t="inlineStr">
+      <c r="AD4" s="23" t="n"/>
+      <c r="AE4" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
+    <row r="5" ht="15" customHeight="1" s="27">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>f003</t>
@@ -1025,7 +1066,11 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Phase IV</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Johnson &amp; Johnson</t>
@@ -1070,21 +1115,25 @@
       <c r="X5" s="5" t="n"/>
       <c r="Y5" s="5" t="n"/>
       <c r="Z5" s="5" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="20" t="n"/>
+      <c r="AA5" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB5" s="19" t="n"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/rilpivirine-2-monthly</t>
         </is>
       </c>
-      <c r="AD5" s="24" t="n"/>
-      <c r="AE5" s="30" t="inlineStr">
+      <c r="AD5" s="23" t="n"/>
+      <c r="AE5" s="25" t="inlineStr">
         <is>
           <t>NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
+    <row r="6" ht="15" customHeight="1" s="27">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>f004</t>
@@ -1122,7 +1171,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>INSTI+NNRTI</t>
+          <t>INSTI + NNRTI</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1163,21 +1212,21 @@
       <c r="X6" s="5" t="n"/>
       <c r="Y6" s="5" t="n"/>
       <c r="Z6" s="5" t="n"/>
-      <c r="AA6" s="19" t="n"/>
-      <c r="AB6" s="20" t="n"/>
+      <c r="AA6" s="18" t="n"/>
+      <c r="AB6" s="19" t="n"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/cabotegravir-rilpivirine</t>
         </is>
       </c>
-      <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="30" t="inlineStr">
+      <c r="AD6" s="23" t="n"/>
+      <c r="AE6" s="25" t="inlineStr">
         <is>
           <t>INSTI + NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
+    <row r="7" ht="15" customHeight="1" s="27">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>f005</t>
@@ -1252,21 +1301,21 @@
       <c r="X7" s="5" t="n"/>
       <c r="Y7" s="5" t="n"/>
       <c r="Z7" s="5" t="n"/>
-      <c r="AA7" s="19" t="n"/>
-      <c r="AB7" s="20" t="n"/>
+      <c r="AA7" s="18" t="n"/>
+      <c r="AB7" s="19" t="n"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lotivibart-n6ls-vh3810109-mab</t>
         </is>
       </c>
-      <c r="AD7" s="24" t="n"/>
-      <c r="AE7" s="30" t="inlineStr">
+      <c r="AD7" s="23" t="n"/>
+      <c r="AE7" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
+    <row r="8" ht="15" customHeight="1" s="27">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>f006</t>
@@ -1341,21 +1390,21 @@
       <c r="X8" s="5" t="n"/>
       <c r="Y8" s="5" t="n"/>
       <c r="Z8" s="5" t="n"/>
-      <c r="AA8" s="19" t="n"/>
-      <c r="AB8" s="20" t="n"/>
+      <c r="AA8" s="18" t="n"/>
+      <c r="AB8" s="19" t="n"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/teropavimab-zinlirvimab</t>
         </is>
       </c>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="30" t="inlineStr">
+      <c r="AD8" s="23" t="n"/>
+      <c r="AE8" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
+    <row r="9" ht="15" customHeight="1" s="27">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>f007</t>
@@ -1434,21 +1483,21 @@
       </c>
       <c r="Y9" s="5" t="n"/>
       <c r="Z9" s="5" t="n"/>
-      <c r="AA9" s="19" t="n"/>
-      <c r="AB9" s="20" t="n"/>
+      <c r="AA9" s="18" t="n"/>
+      <c r="AB9" s="19" t="n"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/tenofovir-lamivudine-dolutegravir-tld-long-acting-injectable-lai-tld-lai</t>
         </is>
       </c>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="30" t="inlineStr">
+      <c r="AD9" s="23" t="n"/>
+      <c r="AE9" s="25" t="inlineStr">
         <is>
           <t>INSTI + NRTI</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
+    <row r="10" ht="15" customHeight="1" s="27">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>f008</t>
@@ -1527,21 +1576,21 @@
       <c r="X10" s="5" t="n"/>
       <c r="Y10" s="5" t="n"/>
       <c r="Z10" s="5" t="n"/>
-      <c r="AA10" s="19" t="n"/>
-      <c r="AB10" s="20" t="n"/>
+      <c r="AA10" s="18" t="n"/>
+      <c r="AB10" s="19" t="n"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/ibalizumab</t>
         </is>
       </c>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="30" t="inlineStr">
+      <c r="AD10" s="23" t="n"/>
+      <c r="AE10" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
+    <row r="11" ht="15" customHeight="1" s="27">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>f009</t>
@@ -1616,21 +1665,21 @@
       <c r="X11" s="5" t="n"/>
       <c r="Y11" s="5" t="n"/>
       <c r="Z11" s="5" t="n"/>
-      <c r="AA11" s="19" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="22" t="inlineStr">
+      <c r="AA11" s="18" t="n"/>
+      <c r="AB11" s="19" t="n"/>
+      <c r="AC11" s="21" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/budigalimab</t>
         </is>
       </c>
-      <c r="AD11" s="24" t="n"/>
-      <c r="AE11" s="30" t="inlineStr">
+      <c r="AD11" s="23" t="n"/>
+      <c r="AE11" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
+    <row r="12" ht="15" customHeight="1" s="27">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>f010</t>
@@ -1709,21 +1758,21 @@
       <c r="X12" s="5" t="n"/>
       <c r="Y12" s="5" t="n"/>
       <c r="Z12" s="5" t="n"/>
-      <c r="AA12" s="19" t="n"/>
-      <c r="AB12" s="20" t="n"/>
+      <c r="AA12" s="18" t="n"/>
+      <c r="AB12" s="19" t="n"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/vrc07-523ls-mab</t>
         </is>
       </c>
-      <c r="AD12" s="24" t="n"/>
-      <c r="AE12" s="30" t="inlineStr">
+      <c r="AD12" s="23" t="n"/>
+      <c r="AE12" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
+    <row r="13" ht="15" customHeight="1" s="27">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>f011</t>
@@ -1761,7 +1810,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I13" s="7" t="n"/>
@@ -1802,21 +1851,25 @@
       </c>
       <c r="Y13" s="5" t="n"/>
       <c r="Z13" s="5" t="n"/>
-      <c r="AA13" s="19" t="n"/>
-      <c r="AB13" s="20" t="n"/>
+      <c r="AA13" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB13" s="19" t="n"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/bictegravir-la</t>
         </is>
       </c>
-      <c r="AD13" s="24" t="n"/>
-      <c r="AE13" s="30" t="inlineStr">
+      <c r="AD13" s="23" t="n"/>
+      <c r="AE13" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
+    <row r="14" ht="15" customHeight="1" s="27">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>f012</t>
@@ -1849,12 +1902,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>ViiV Healthcare; Gilead</t>
+          <t>ViiV Healthcare; Gilead (investigator led)</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>INSTI+capsid inhibitor</t>
+          <t>INSTI + capsid inhibitor</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1899,21 +1952,21 @@
       <c r="X14" s="5" t="n"/>
       <c r="Y14" s="5" t="n"/>
       <c r="Z14" s="5" t="n"/>
-      <c r="AA14" s="19" t="n"/>
-      <c r="AB14" s="20" t="n"/>
+      <c r="AA14" s="18" t="n"/>
+      <c r="AB14" s="19" t="n"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/cabotegravir-lenacapavir</t>
         </is>
       </c>
-      <c r="AD14" s="24" t="n"/>
-      <c r="AE14" s="30" t="inlineStr">
+      <c r="AD14" s="23" t="n"/>
+      <c r="AE14" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor + INSTI</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
+    <row r="15" ht="15" customHeight="1" s="27">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>f013</t>
@@ -1926,7 +1979,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>MK-8591D (Islatravir and Lenacapavir)</t>
+          <t>Islatravir + Lenacapavir (MK-8591D)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1984,21 +2037,21 @@
       <c r="X15" s="5" t="n"/>
       <c r="Y15" s="5" t="n"/>
       <c r="Z15" s="5" t="n"/>
-      <c r="AA15" s="19" t="n"/>
-      <c r="AB15" s="20" t="n"/>
+      <c r="AA15" s="18" t="n"/>
+      <c r="AB15" s="19" t="n"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/mk-8591d-islatravir-and-lenacapavir</t>
         </is>
       </c>
-      <c r="AD15" s="24" t="n"/>
-      <c r="AE15" s="30" t="inlineStr">
+      <c r="AD15" s="23" t="n"/>
+      <c r="AE15" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor + NRTTI</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
+    <row r="16" ht="15" customHeight="1" s="27">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>f014</t>
@@ -2016,7 +2069,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Prevention</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2036,7 +2089,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I16" s="7" t="n"/>
@@ -2069,21 +2122,21 @@
       <c r="X16" s="5" t="n"/>
       <c r="Y16" s="5" t="n"/>
       <c r="Z16" s="5" t="n"/>
-      <c r="AA16" s="19" t="n"/>
-      <c r="AB16" s="20" t="n"/>
+      <c r="AA16" s="18" t="n"/>
+      <c r="AB16" s="19" t="n"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/cabotegravir-4-monthly-q4m</t>
         </is>
       </c>
-      <c r="AD16" s="24" t="n"/>
-      <c r="AE16" s="30" t="inlineStr">
+      <c r="AD16" s="23" t="n"/>
+      <c r="AE16" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
+    <row r="17" ht="15" customHeight="1" s="27">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>f015</t>
@@ -2158,21 +2211,21 @@
       </c>
       <c r="Y17" s="5" t="n"/>
       <c r="Z17" s="5" t="n"/>
-      <c r="AA17" s="19" t="n"/>
-      <c r="AB17" s="20" t="n"/>
+      <c r="AA17" s="18" t="n"/>
+      <c r="AB17" s="19" t="n"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/rilpivirine-prodrug-nanoformulation-nm3rpv</t>
         </is>
       </c>
-      <c r="AD17" s="24" t="n"/>
-      <c r="AE17" s="30" t="inlineStr">
+      <c r="AD17" s="23" t="n"/>
+      <c r="AE17" s="25" t="inlineStr">
         <is>
           <t>NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="26">
+    <row r="18" ht="15" customHeight="1" s="27">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>f016</t>
@@ -2243,21 +2296,21 @@
       </c>
       <c r="Y18" s="5" t="n"/>
       <c r="Z18" s="5" t="n"/>
-      <c r="AA18" s="19" t="n"/>
-      <c r="AB18" s="20" t="n"/>
+      <c r="AA18" s="18" t="n"/>
+      <c r="AB18" s="19" t="n"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/bictegravir-la</t>
         </is>
       </c>
-      <c r="AD18" s="24" t="n"/>
-      <c r="AE18" s="30" t="inlineStr">
+      <c r="AD18" s="23" t="n"/>
+      <c r="AE18" s="25" t="inlineStr">
         <is>
           <t>NRTI</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="26">
+    <row r="19" ht="15" customHeight="1" s="27">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>f017</t>
@@ -2328,21 +2381,21 @@
       <c r="X19" s="5" t="n"/>
       <c r="Y19" s="5" t="n"/>
       <c r="Z19" s="5" t="n"/>
-      <c r="AA19" s="19" t="n"/>
-      <c r="AB19" s="20" t="n"/>
+      <c r="AA19" s="18" t="n"/>
+      <c r="AB19" s="19" t="n"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lenacapavir-once-yearly</t>
         </is>
       </c>
-      <c r="AD19" s="24" t="n"/>
-      <c r="AE19" s="30" t="inlineStr">
+      <c r="AD19" s="23" t="n"/>
+      <c r="AE19" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="26">
+    <row r="20" ht="15" customHeight="1" s="27">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>f018</t>
@@ -2360,7 +2413,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Prevention</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2380,7 +2433,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I20" s="7" t="n"/>
@@ -2413,21 +2466,25 @@
       <c r="X20" s="5" t="n"/>
       <c r="Y20" s="5" t="n"/>
       <c r="Z20" s="5" t="n"/>
-      <c r="AA20" s="19" t="n"/>
-      <c r="AB20" s="20" t="n"/>
+      <c r="AA20" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB20" s="19" t="n"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/cabotegravir-ph20</t>
         </is>
       </c>
-      <c r="AD20" s="24" t="n"/>
-      <c r="AE20" s="30" t="inlineStr">
+      <c r="AD20" s="23" t="n"/>
+      <c r="AE20" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="26">
+    <row r="21" ht="15" customHeight="1" s="27">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>f019</t>
@@ -2514,21 +2571,21 @@
       <c r="X21" s="5" t="n"/>
       <c r="Y21" s="5" t="n"/>
       <c r="Z21" s="5" t="n"/>
-      <c r="AA21" s="19" t="n"/>
-      <c r="AB21" s="20" t="n"/>
+      <c r="AA21" s="18" t="n"/>
+      <c r="AB21" s="19" t="n"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/vrc01-mab</t>
         </is>
       </c>
-      <c r="AD21" s="24" t="n"/>
-      <c r="AE21" s="30" t="inlineStr">
+      <c r="AD21" s="23" t="n"/>
+      <c r="AE21" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="26">
+    <row r="22" ht="15" customHeight="1" s="27">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>f020</t>
@@ -2541,7 +2598,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>MK-8591B (islatravir + ulonivirine)</t>
+          <t>islatravir + Ulonivirine (MK-8591B)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2599,21 +2656,21 @@
       <c r="X22" s="5" t="n"/>
       <c r="Y22" s="5" t="n"/>
       <c r="Z22" s="5" t="n"/>
-      <c r="AA22" s="19" t="n"/>
-      <c r="AB22" s="20" t="n"/>
+      <c r="AA22" s="18" t="n"/>
+      <c r="AB22" s="19" t="n"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/mk-8591b-islatravir-ulonivirine</t>
         </is>
       </c>
-      <c r="AD22" s="24" t="n"/>
-      <c r="AE22" s="30" t="inlineStr">
+      <c r="AD22" s="23" t="n"/>
+      <c r="AE22" s="25" t="inlineStr">
         <is>
           <t>NRTTI + NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="26">
+    <row r="23" ht="15" customHeight="1" s="27">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>f021</t>
@@ -2688,21 +2745,21 @@
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="5" t="n"/>
       <c r="Z23" s="5" t="n"/>
-      <c r="AA23" s="19" t="n"/>
-      <c r="AB23" s="20" t="n"/>
+      <c r="AA23" s="18" t="n"/>
+      <c r="AB23" s="19" t="n"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/vh-280-vh-4004280</t>
         </is>
       </c>
-      <c r="AD23" s="24" t="n"/>
-      <c r="AE23" s="30" t="inlineStr">
+      <c r="AD23" s="23" t="n"/>
+      <c r="AE23" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="26">
+    <row r="24" ht="15" customHeight="1" s="27">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>f022</t>
@@ -2773,21 +2830,21 @@
       <c r="X24" s="5" t="n"/>
       <c r="Y24" s="5" t="n"/>
       <c r="Z24" s="5" t="n"/>
-      <c r="AA24" s="19" t="n"/>
-      <c r="AB24" s="20" t="n"/>
+      <c r="AA24" s="18" t="n"/>
+      <c r="AB24" s="19" t="n"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/pgt-121-mab</t>
         </is>
       </c>
-      <c r="AD24" s="24" t="n"/>
-      <c r="AE24" s="30" t="inlineStr">
+      <c r="AD24" s="23" t="n"/>
+      <c r="AE24" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="26">
+    <row r="25" ht="15" customHeight="1" s="27">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>f023</t>
@@ -2862,21 +2919,21 @@
       <c r="X25" s="5" t="n"/>
       <c r="Y25" s="5" t="n"/>
       <c r="Z25" s="5" t="n"/>
-      <c r="AA25" s="19" t="n"/>
-      <c r="AB25" s="20" t="n"/>
+      <c r="AA25" s="18" t="n"/>
+      <c r="AB25" s="19" t="n"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/pgdm1400-mab</t>
         </is>
       </c>
-      <c r="AD25" s="24" t="n"/>
-      <c r="AE25" s="30" t="inlineStr">
+      <c r="AD25" s="23" t="n"/>
+      <c r="AE25" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="26">
+    <row r="26" ht="15" customHeight="1" s="27">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>f024</t>
@@ -2914,7 +2971,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>protease inhibitors (PI) + nucleotide analog reverse-transcriptase inhibitor (NRTI)</t>
+          <t>PI + NRTI</t>
         </is>
       </c>
       <c r="I26" s="7" t="n"/>
@@ -2928,11 +2985,7 @@
       <c r="M26" s="7" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="8" t="n"/>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P26" s="8" t="n"/>
       <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>x</t>
@@ -2951,21 +3004,21 @@
       <c r="X26" s="5" t="n"/>
       <c r="Y26" s="5" t="n"/>
       <c r="Z26" s="5" t="n"/>
-      <c r="AA26" s="19" t="n"/>
-      <c r="AB26" s="20" t="n"/>
+      <c r="AA26" s="18" t="n"/>
+      <c r="AB26" s="19" t="n"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lopinavir-ritonavir-and-tenofovir-lrt-tlc-art-101</t>
         </is>
       </c>
-      <c r="AD26" s="24" t="n"/>
-      <c r="AE26" s="30" t="inlineStr">
+      <c r="AD26" s="23" t="n"/>
+      <c r="AE26" s="25" t="inlineStr">
         <is>
           <t>NRTI + PI</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="26">
+    <row r="27" ht="15" customHeight="1" s="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>f025</t>
@@ -3003,7 +3056,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>prodrug of bictegravir (integrase strand transfer inhibitor; INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I27" s="7" t="n"/>
@@ -3040,21 +3093,25 @@
       </c>
       <c r="Y27" s="5" t="n"/>
       <c r="Z27" s="5" t="n"/>
-      <c r="AA27" s="19" t="n"/>
-      <c r="AB27" s="20" t="n"/>
+      <c r="AA27" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB27" s="19" t="n"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/ultra-long-acting-dimeric-bictegravir-prodrug</t>
         </is>
       </c>
-      <c r="AD27" s="24" t="n"/>
-      <c r="AE27" s="30" t="inlineStr">
+      <c r="AD27" s="23" t="n"/>
+      <c r="AE27" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="26">
+    <row r="28" ht="15" customHeight="1" s="27">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>f026</t>
@@ -3129,21 +3186,21 @@
       <c r="X28" s="5" t="n"/>
       <c r="Y28" s="5" t="n"/>
       <c r="Z28" s="5" t="n"/>
-      <c r="AA28" s="19" t="n"/>
-      <c r="AB28" s="20" t="n"/>
+      <c r="AA28" s="18" t="n"/>
+      <c r="AB28" s="19" t="n"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lenacapavir-teropavimab-zinlirvimab</t>
         </is>
       </c>
-      <c r="AD28" s="24" t="n"/>
-      <c r="AE28" s="30" t="inlineStr">
+      <c r="AD28" s="23" t="n"/>
+      <c r="AE28" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor + mAb</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="26">
+    <row r="29" ht="15" customHeight="1" s="27">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>f027</t>
@@ -3222,21 +3279,21 @@
       <c r="X29" s="5" t="n"/>
       <c r="Y29" s="5" t="n"/>
       <c r="Z29" s="5" t="n"/>
-      <c r="AA29" s="19" t="n"/>
-      <c r="AB29" s="20" t="n"/>
+      <c r="AA29" s="18" t="n"/>
+      <c r="AB29" s="19" t="n"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/pgt121414ls-vrc07-523ls-mab</t>
         </is>
       </c>
-      <c r="AD29" s="24" t="n"/>
-      <c r="AE29" s="30" t="inlineStr">
+      <c r="AD29" s="23" t="n"/>
+      <c r="AE29" s="25" t="inlineStr">
         <is>
           <t>mAb</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="26">
+    <row r="30" ht="15" customHeight="1" s="27">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>f028</t>
@@ -3274,7 +3331,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>INSTI+capsid inhibitor</t>
+          <t>INSTI + capsid inhibitor</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -3307,21 +3364,25 @@
       <c r="X30" s="5" t="n"/>
       <c r="Y30" s="5" t="n"/>
       <c r="Z30" s="5" t="n"/>
-      <c r="AA30" s="19" t="n"/>
-      <c r="AB30" s="20" t="n"/>
+      <c r="AA30" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB30" s="19" t="n"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/lepetegravir-lenacapavir-pacfosacil-gs-1720gs-4182</t>
         </is>
       </c>
-      <c r="AD30" s="24" t="n"/>
-      <c r="AE30" s="30" t="inlineStr">
+      <c r="AD30" s="23" t="n"/>
+      <c r="AE30" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor + INSTI</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="26">
+    <row r="31" ht="15" customHeight="1" s="27">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>f029</t>
@@ -3359,7 +3420,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Second-generation Integrase Strand Transfer Inhibitors (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I31" s="7" t="n"/>
@@ -3392,21 +3453,25 @@
       </c>
       <c r="Y31" s="5" t="n"/>
       <c r="Z31" s="5" t="n"/>
-      <c r="AA31" s="19" t="n"/>
-      <c r="AB31" s="20" t="n"/>
+      <c r="AA31" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB31" s="19" t="n"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>https://lapal.ch/formulations/bictegravir-plga-nanoformulation</t>
         </is>
       </c>
-      <c r="AD31" s="24" t="n"/>
-      <c r="AE31" s="30" t="inlineStr">
+      <c r="AD31" s="23" t="n"/>
+      <c r="AE31" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="26">
+    <row r="32" ht="15" customHeight="1" s="27">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>c030</t>
@@ -3424,7 +3489,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Treatment</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3477,21 +3542,21 @@
       <c r="X32" s="5" t="n"/>
       <c r="Y32" s="5" t="n"/>
       <c r="Z32" s="5" t="n"/>
-      <c r="AA32" s="19" t="n"/>
-      <c r="AB32" s="20" t="n"/>
+      <c r="AA32" s="18" t="n"/>
+      <c r="AB32" s="19" t="n"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/ulonivirine-mk-8507</t>
         </is>
       </c>
-      <c r="AD32" s="24" t="n"/>
-      <c r="AE32" s="30" t="inlineStr">
+      <c r="AD32" s="23" t="n"/>
+      <c r="AE32" s="25" t="inlineStr">
         <is>
           <t>NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="26">
+    <row r="33" ht="15" customHeight="1" s="27">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>c032</t>
@@ -3529,7 +3594,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -3562,21 +3627,21 @@
       <c r="X33" s="5" t="n"/>
       <c r="Y33" s="5" t="n"/>
       <c r="Z33" s="5" t="n"/>
-      <c r="AA33" s="19" t="n"/>
-      <c r="AB33" s="20" t="n"/>
+      <c r="AA33" s="18" t="n"/>
+      <c r="AB33" s="19" t="n"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/lepetegravir-gs-1720</t>
         </is>
       </c>
-      <c r="AD33" s="24" t="n"/>
-      <c r="AE33" s="30" t="inlineStr">
+      <c r="AD33" s="23" t="n"/>
+      <c r="AE33" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="26">
+    <row r="34" ht="15" customHeight="1" s="27">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>c033</t>
@@ -3614,7 +3679,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>integrase strand transfer inhibitor; INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -3659,21 +3724,21 @@
       <c r="X34" s="5" t="n"/>
       <c r="Y34" s="5" t="n"/>
       <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="19" t="n"/>
-      <c r="AB34" s="20" t="n"/>
+      <c r="AA34" s="18" t="n"/>
+      <c r="AB34" s="19" t="n"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/cabotegravir</t>
         </is>
       </c>
-      <c r="AD34" s="24" t="n"/>
-      <c r="AE34" s="30" t="inlineStr">
+      <c r="AD34" s="23" t="n"/>
+      <c r="AE34" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="26">
+    <row r="35" ht="15" customHeight="1" s="27">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>c034</t>
@@ -3748,21 +3813,21 @@
       <c r="X35" s="5" t="n"/>
       <c r="Y35" s="5" t="n"/>
       <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="19" t="n"/>
-      <c r="AB35" s="20" t="n"/>
+      <c r="AA35" s="18" t="n"/>
+      <c r="AB35" s="19" t="n"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/islatravir-isl</t>
         </is>
       </c>
-      <c r="AD35" s="24" t="n"/>
-      <c r="AE35" s="30" t="inlineStr">
+      <c r="AD35" s="23" t="n"/>
+      <c r="AE35" s="25" t="inlineStr">
         <is>
           <t>NRTTI</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="26">
+    <row r="36" ht="15" customHeight="1" s="27">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>c035</t>
@@ -3788,7 +3853,11 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Phase IV</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Population Council</t>
@@ -3833,21 +3902,21 @@
         </is>
       </c>
       <c r="Z36" s="5" t="n"/>
-      <c r="AA36" s="19" t="n"/>
-      <c r="AB36" s="20" t="n"/>
+      <c r="AA36" s="18" t="n"/>
+      <c r="AB36" s="19" t="n"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>https://lapal.ch/technology/dapivirine-monthly-vaginal-ring</t>
         </is>
       </c>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="30" t="inlineStr">
+      <c r="AD36" s="23" t="n"/>
+      <c r="AE36" s="25" t="inlineStr">
         <is>
           <t>NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="26">
+    <row r="37" ht="15" customHeight="1" s="27">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>c037</t>
@@ -3885,7 +3954,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Prodrug of cabotegravir (integrase strand transfer inhibitor (INSTI))</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I37" s="7" t="n"/>
@@ -3930,21 +3999,21 @@
       </c>
       <c r="Y37" s="5" t="n"/>
       <c r="Z37" s="5" t="n"/>
-      <c r="AA37" s="19" t="n"/>
-      <c r="AB37" s="20" t="n"/>
+      <c r="AA37" s="18" t="n"/>
+      <c r="AB37" s="19" t="n"/>
       <c r="AC37" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/vh-310-vh-4367310</t>
         </is>
       </c>
-      <c r="AD37" s="24" t="n"/>
-      <c r="AE37" s="30" t="inlineStr">
+      <c r="AD37" s="23" t="n"/>
+      <c r="AE37" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="26">
+    <row r="38" ht="15" customHeight="1" s="27">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>c038</t>
@@ -3982,7 +4051,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>Prodrug of lenacapavir (capsid inhibitor)</t>
+          <t>capsid inhibitor</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -4015,21 +4084,25 @@
       <c r="X38" s="5" t="n"/>
       <c r="Y38" s="5" t="n"/>
       <c r="Z38" s="5" t="n"/>
-      <c r="AA38" s="19" t="n"/>
-      <c r="AB38" s="20" t="n"/>
+      <c r="AA38" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB38" s="19" t="n"/>
       <c r="AC38" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/lenacapavir-pacfosacil-gs-4182</t>
         </is>
       </c>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="30" t="inlineStr">
+      <c r="AD38" s="23" t="n"/>
+      <c r="AE38" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="26">
+    <row r="39" ht="15" customHeight="1" s="27">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>c039</t>
@@ -4112,21 +4185,25 @@
       <c r="X39" s="5" t="n"/>
       <c r="Y39" s="5" t="n"/>
       <c r="Z39" s="5" t="n"/>
-      <c r="AA39" s="19" t="n"/>
-      <c r="AB39" s="20" t="n"/>
+      <c r="AA39" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB39" s="19" t="n"/>
       <c r="AC39" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/lenacapavir-len</t>
         </is>
       </c>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="30" t="inlineStr">
+      <c r="AD39" s="23" t="n"/>
+      <c r="AE39" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="26">
+    <row r="40" ht="15" customHeight="1" s="27">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>c040</t>
@@ -4164,7 +4241,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>Integrase Strand Transfer Inhibitors (INSTIs)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -4205,21 +4282,21 @@
       <c r="X40" s="5" t="n"/>
       <c r="Y40" s="5" t="n"/>
       <c r="Z40" s="5" t="n"/>
-      <c r="AA40" s="19" t="n"/>
-      <c r="AB40" s="20" t="n"/>
+      <c r="AA40" s="18" t="n"/>
+      <c r="AB40" s="19" t="n"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/gs-3242</t>
         </is>
       </c>
-      <c r="AD40" s="24" t="n"/>
-      <c r="AE40" s="30" t="inlineStr">
+      <c r="AD40" s="23" t="n"/>
+      <c r="AE40" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="26">
+    <row r="41" ht="15" customHeight="1" s="27">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>c041</t>
@@ -4252,12 +4329,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>ViiV Healthcare; Shionogi</t>
+          <t>ViiV Healthcare</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>HIV-1 Capsid inhibitor</t>
+          <t>Capsid inhibitor</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -4306,21 +4383,21 @@
       <c r="X41" s="5" t="n"/>
       <c r="Y41" s="5" t="n"/>
       <c r="Z41" s="5" t="n"/>
-      <c r="AA41" s="19" t="n"/>
-      <c r="AB41" s="20" t="n"/>
+      <c r="AA41" s="18" t="n"/>
+      <c r="AB41" s="19" t="n"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/vh-499-vh-4011499</t>
         </is>
       </c>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="30" t="inlineStr">
+      <c r="AD41" s="23" t="n"/>
+      <c r="AE41" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="26">
+    <row r="42" ht="15" customHeight="1" s="27">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>c042</t>
@@ -4353,12 +4430,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>ViiV Healthcare; Shionogi</t>
+          <t>ViiV Healthcare</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Integrase strand transfer inhibitor (INSTI)</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -4407,21 +4484,21 @@
       <c r="X42" s="5" t="n"/>
       <c r="Y42" s="5" t="n"/>
       <c r="Z42" s="5" t="n"/>
-      <c r="AA42" s="19" t="n"/>
-      <c r="AB42" s="20" t="n"/>
+      <c r="AA42" s="18" t="n"/>
+      <c r="AB42" s="19" t="n"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/vh-184-vh-4524184</t>
         </is>
       </c>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="30" t="inlineStr">
+      <c r="AD42" s="23" t="n"/>
+      <c r="AE42" s="25" t="inlineStr">
         <is>
           <t>INSTI</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="26">
+    <row r="43" ht="15" customHeight="1" s="27">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>c043</t>
@@ -4492,21 +4569,25 @@
       <c r="X43" s="5" t="n"/>
       <c r="Y43" s="5" t="n"/>
       <c r="Z43" s="5" t="n"/>
-      <c r="AA43" s="19" t="n"/>
-      <c r="AB43" s="20" t="n"/>
+      <c r="AA43" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB43" s="19" t="n"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/depulfavirine-nanosphere-lai</t>
         </is>
       </c>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="30" t="inlineStr">
+      <c r="AD43" s="23" t="n"/>
+      <c r="AE43" s="25" t="inlineStr">
         <is>
           <t>NNRTI</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="26">
+    <row r="44" ht="15" customHeight="1" s="27">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>c044</t>
@@ -4544,7 +4625,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>nucleoside reverse transcriptase translocation inhibitor (NRTTI)</t>
+          <t>NRTTI</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -4577,21 +4658,21 @@
       <c r="X44" s="5" t="n"/>
       <c r="Y44" s="5" t="n"/>
       <c r="Z44" s="5" t="n"/>
-      <c r="AA44" s="19" t="n"/>
-      <c r="AB44" s="20" t="n"/>
+      <c r="AA44" s="18" t="n"/>
+      <c r="AB44" s="19" t="n"/>
       <c r="AC44" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/alimatravir-mk-8527</t>
         </is>
       </c>
-      <c r="AD44" s="24" t="n"/>
-      <c r="AE44" s="30" t="inlineStr">
+      <c r="AD44" s="23" t="n"/>
+      <c r="AE44" s="25" t="inlineStr">
         <is>
           <t>NRTTI</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="26">
+    <row r="45" ht="15" customHeight="1" s="27">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>c045</t>
@@ -4609,7 +4690,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Treatment</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -4666,65 +4747,256 @@
       </c>
       <c r="Y45" s="5" t="n"/>
       <c r="Z45" s="5" t="n"/>
-      <c r="AA45" s="19" t="n"/>
-      <c r="AB45" s="20" t="n"/>
+      <c r="AA45" s="18" t="n"/>
+      <c r="AB45" s="19" t="n"/>
       <c r="AC45" t="inlineStr">
         <is>
           <t>https://lapal.ch/compounds/gs-3107</t>
         </is>
       </c>
-      <c r="AD45" s="24" t="n"/>
-      <c r="AE45" s="30" t="inlineStr">
+      <c r="AD45" s="23" t="n"/>
+      <c r="AE45" s="25" t="inlineStr">
         <is>
           <t>Capsid inhibitor</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48" ht="15" customHeight="1" s="26">
-      <c r="Z48" s="9" t="inlineStr">
-        <is>
-          <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
-        </is>
-      </c>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>f030</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>formulations</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GS-3242 + lenacapavir</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Phase II</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Gilead</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>INSTI + capsid inhibitor</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr">
+        <is>
+          <t>manually confirmed</t>
+        </is>
+      </c>
+      <c r="AE46" s="5" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1" s="27">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>f031</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>formulations</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VH-184+VH-499 </t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Early-stage</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Phase I</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>ViiV Healthcare</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>INSTI + capsid inhibitor</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr">
+        <is>
+          <t>manually confirmed</t>
+        </is>
+      </c>
+      <c r="AE47" s="5" t="inlineStr">
+        <is>
+          <t>Capsid inhibitor + INSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="27">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>f032</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>formulations</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Cabotegravir + rilpivirine 3 times a year (CAB 4M + RPV 4M)</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Late-stage</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Phase II/III</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>ViiV Healthcare; Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>INSTI + NNRTI</t>
+        </is>
+      </c>
+      <c r="K48" s="32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>manually confirmed</t>
+        </is>
+      </c>
+      <c r="AE48" s="5" t="inlineStr">
+        <is>
+          <t>INSTI + NNRTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="E49" s="5" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:AE2"/>
   <mergeCells count="3">
     <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:V1"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation sqref="B3:B45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose formulations or compounds" prompt="Choose formulations or compounds" type="list">
+    <dataValidation sqref="B3:B48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose formulations or compounds" prompt="Choose formulations or compounds" type="list">
       <formula1>"formulations,compounds"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D3:D45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Treatment, Prevention or Both" prompt="Treatment, Prevention or Both" type="list">
+    <dataValidation sqref="D3:D48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Treatment, Prevention or Both" prompt="Treatment, Prevention or Both" type="list">
       <formula1>"Treatment,Prevention,Both"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E3:E45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a development stage" prompt="Pick a development stage" type="list">
+    <dataValidation sqref="E3:E49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a development stage" prompt="Pick a development stage" type="list">
       <formula1>"Approved,Late-stage,Early-stage,Not stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F3:F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Highest clinical phase" prompt="Highest clinical phase" type="list">
-      <formula1>"Preclinical,Phase I,Phase I/II,Phase II,Phase II/III,Phase III,Phase IV"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="W3:W45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Where the interval came from" prompt="Where the interval came from" type="list">
+    <dataValidation sqref="W3:W48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Where the interval came from" prompt="Where the interval came from" type="list">
       <formula1>"LAPaL record,derived from trials,manually confirmed,not stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="I3:V45 X3:Y45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type x to mark, or leave blank" prompt="Type x to mark, or leave blank" type="list">
+    <dataValidation sqref="I3:V45 I46 K46:K47 T47 U46:U47 X3:Y45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Type x to mark, or leave blank" prompt="Type x to mark, or leave blank" type="list">
       <formula1>"x"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="AA3:AA48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Leave blank to show the entry. Type x to hide it from the dashboard." prompt="Leave blank to show the entry. Type x to hide it from the dashboard." type="list">
       <formula1>"x"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE3:AE48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a class, or a combination for a multi-class product." prompt="Pick a class, or a combination for a multi-class product." type="list">
+    <dataValidation sqref="AE3:AE45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a class, or a combination for a multi-class product." prompt="Pick a class, or a combination for a multi-class product." type="list">
       <formula1>"Capsid inhibitor,INSTI,NNRTI,NRTI,NRTTI,mAb,PI,Fusion inhibitor,Capsid inhibitor + INSTI,Capsid inhibitor + NRTTI,Capsid inhibitor + mAb,INSTI + NNRTI,INSTI + NRTI,NRTI + PI,NRTTI + NNRTI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Highest clinical phase" prompt="Highest clinical phase" type="list">
+      <formula1>"Preclinical,Phase I,Phase I/II,Phase II,Phase II/III,Phase III,Phase IV"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -4741,338 +5013,345 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="26" min="1" max="1"/>
-    <col width="88" customWidth="1" style="26" min="2" max="2"/>
+    <col width="26" customWidth="1" style="27" min="1" max="1"/>
+    <col width="88" customWidth="1" style="27" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.25" customHeight="1" s="26">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="16.25" customHeight="1" s="27">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>LAPaL long-acting HIV</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Curation sheet for the interactive dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="26">
-      <c r="A2" s="12" t="n"/>
-      <c r="B2" s="13" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="26">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="27">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="27">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B3" s="14" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="27">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>1. Edit the Entries tab</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>One row per product. Change any white cell. Add or delete whole rows freely; order does not matter.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="27">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2. Save the file</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Keep it as .xlsx.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="39" customHeight="1" s="26">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="39" customHeight="1" s="27">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>3. Run the build step</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>In a terminal:  python build_data.py hiv_curation.xlsx  → writes hiv_dashboard_data.json, which the dashboard reads.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="23.75" customHeight="1" s="26">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="7" ht="23.75" customHeight="1" s="27">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4. Refresh the dashboard</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>The new data appears. The build step prints a check report and refuses to write if something essential is missing.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="27">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="27">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>COLUMNS</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="27">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Leave as is. Leave blank for a new row and the build step assigns one.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="27">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>band</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>formulations = a discrete long-acting product. compounds = an underlying molecule in LA development.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="27">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Product or molecule name, shown on the dashboard.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="23.75" customHeight="1" s="26">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="13" ht="23.75" customHeight="1" s="27">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>indication</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Treatment, Prevention, or Both. Drives which selection the row appears under. "Both" shows it once, tagged for both.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="27">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Approved / Late-stage / Early-stage / Not stated. Sets the row colour and grouping.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="27">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>highest_phase</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Highest clinical phase on record. Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="27">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>developers</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>One or more, separated by a semicolon ( ; ).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="27">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>drug_class</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="23.75" customHeight="1" s="26">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="23.75" customHeight="1" s="27">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>ROUTE columns</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Mark x under every route that applies. PO oral, SC subcutaneous, IM intramuscular, IV intravenous, VR vaginal ring, TD transdermal.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="23.75" customHeight="1" s="26">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="19" ht="23.75" customHeight="1" s="27">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>INTERVAL columns</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Mark x under every dosing interval studied. 1W weekly, 2W 2-weekly, 1M monthly, 2M, 3M, 4M, 6M, 12M yearly. Leave all blank if unknown; the row then sits in the "not stated" lane. Do not enter daily or single-dose.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="23.75" customHeight="1" s="26">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="20" ht="23.75" customHeight="1" s="27">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>frequency_source</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>LAPaL record = confirmed. "derived from trials" = filled from a linked trial and shown with a dagger until you confirm. Change to "manually confirmed" once checked.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="26">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="27">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>flag_no_trials</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Mark x if no clinical trials are linked in LAPaL. Surfaced in the data-quality panel.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="26">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="27">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>flag_no_reg_rows</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Mark x if approved but missing structured regulatory rows. Surfaced in the data-quality panel.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="26">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="27">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>curator_notes</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Free text for you. Not shown on the dashboard.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="26">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="26">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="27">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="27">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>AUTOMATIC FLAGS</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>The build step computes these; you do not enter them:</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="27">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>missing_frequency</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>set when no interval x is marked.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="23.75" customHeight="1" s="26">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="27" ht="23.75" customHeight="1" s="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>conventional_approval_only</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>set when stage is Approved, no interval is marked, and the only route is oral (an approved conventional drug shown as an API in LA development).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="26">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="26">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="27">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="27">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>RULES THE BUILD STEP CHECKS</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="26">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="B29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="27">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>every row needs</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>a band, a name, an indication and a stage. Missing any of these stops the build with a clear message.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="26">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="27">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>controlled values</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>band, stage, indication and interval codes must match the lists above. Typos are reported by row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1" s="27">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
         </is>
       </c>
     </row>

--- a/hiv_curation.xlsx
+++ b/hiv_curation.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -159,8 +159,17 @@
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF12161C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF12161C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -237,6 +246,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,7 +338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -396,6 +410,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5013,7 +5031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="27" min="1" max="1"/>
@@ -5033,282 +5051,271 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="27">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="12" t="n"/>
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>SETTINGS</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="27">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Default view</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>Dosing timeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="27">
+      <c r="A4" s="36" t="n"/>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>Which view opens first when someone loads the dashboard. Pick one from the dropdown; leave blank to keep Dosing timeline. Run build_data.py afterwards, same as any other change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="27"/>
+    <row r="6" ht="39" customHeight="1" s="27">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="n"/>
+    </row>
+    <row r="7" ht="23.75" customHeight="1" s="27">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="27">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="27">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>1. Edit the Entries tab</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>One row per product. Change any white cell. Add or delete whole rows freely; order does not matter.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="27">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="27">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>2. Save the file</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Keep it as .xlsx.</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="39" customHeight="1" s="27">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>3. Run the build step</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>In a terminal:  python build_data.py hiv_curation.xlsx  → writes hiv_dashboard_data.json, which the dashboard reads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="23.75" customHeight="1" s="27">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>4. Refresh the dashboard</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>The new data appears. The build step prints a check report and refuses to write if something essential is missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="27">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>COLUMNS</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="27">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>3. Run the build step</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Leave as is. Leave blank for a new row and the build step assigns one.</t>
+          <t>In a terminal:  python build_data.py hiv_curation.xlsx  → writes hiv_dashboard_data.json, which the dashboard reads.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="27">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>band</t>
+          <t>4. Refresh the dashboard</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>formulations = a discrete long-acting product. compounds = an underlying molecule in LA development.</t>
+          <t>The new data appears. The build step prints a check report and refuses to write if something essential is missing.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="27">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Product or molecule name, shown on the dashboard.</t>
-        </is>
-      </c>
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="n"/>
     </row>
     <row r="13" ht="23.75" customHeight="1" s="27">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>indication</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Treatment, Prevention, or Both. Drives which selection the row appears under. "Both" shows it once, tagged for both.</t>
-        </is>
-      </c>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>COLUMNS</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="27">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Approved / Late-stage / Early-stage / Not stated. Sets the row colour and grouping.</t>
+          <t>Leave as is. Leave blank for a new row and the build step assigns one.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="27">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>highest_phase</t>
+          <t>band</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Highest clinical phase on record. Optional, shown in the tooltip.</t>
+          <t>formulations = a discrete long-acting product. compounds = an underlying molecule in LA development.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="27">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>developers</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>One or more, separated by a semicolon ( ; ).</t>
+          <t>Product or molecule name, shown on the dashboard.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="27">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>indication</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Optional, shown in the tooltip.</t>
+          <t>Treatment, Prevention, or Both. Drives which selection the row appears under. "Both" shows it once, tagged for both.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="23.75" customHeight="1" s="27">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ROUTE columns</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Mark x under every route that applies. PO oral, SC subcutaneous, IM intramuscular, IV intravenous, VR vaginal ring, TD transdermal.</t>
+          <t>Approved / Late-stage / Early-stage / Not stated. Sets the row colour and grouping.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="23.75" customHeight="1" s="27">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>INTERVAL columns</t>
+          <t>highest_phase</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Mark x under every dosing interval studied. 1W weekly, 2W 2-weekly, 1M monthly, 2M, 3M, 4M, 6M, 12M yearly. Leave all blank if unknown; the row then sits in the "not stated" lane. Do not enter daily or single-dose.</t>
+          <t>Highest clinical phase on record. Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="23.75" customHeight="1" s="27">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>frequency_source</t>
+          <t>developers</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>LAPaL record = confirmed. "derived from trials" = filled from a linked trial and shown with a dagger until you confirm. Change to "manually confirmed" once checked.</t>
+          <t>One or more, separated by a semicolon ( ; ).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="27">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>flag_no_trials</t>
+          <t>drug_class</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Mark x if no clinical trials are linked in LAPaL. Surfaced in the data-quality panel.</t>
+          <t>Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="27">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>flag_no_reg_rows</t>
+          <t>ROUTE columns</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Mark x if approved but missing structured regulatory rows. Surfaced in the data-quality panel.</t>
+          <t>Mark x under every route that applies. PO oral, SC subcutaneous, IM intramuscular, IV intravenous, VR vaginal ring, TD transdermal.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="27">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>curator_notes</t>
+          <t>INTERVAL columns</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Free text for you. Not shown on the dashboard.</t>
+          <t>Mark x under every dosing interval studied. 1W weekly, 2W 2-weekly, 1M monthly, 2M, 3M, 4M, 6M, 12M yearly. Leave all blank if unknown; the row then sits in the "not stated" lane. Do not enter daily or single-dose.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="27">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="12" t="n"/>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>frequency_source</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>LAPaL record = confirmed. "derived from trials" = filled from a linked trial and shown with a dagger until you confirm. Change to "manually confirmed" once checked.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="27">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>AUTOMATIC FLAGS</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>The build step computes these; you do not enter them:</t>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>flag_no_trials</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Mark x if no clinical trials are linked in LAPaL. Surfaced in the data-quality panel.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="27">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>missing_frequency</t>
+          <t>flag_no_reg_rows</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>set when no interval x is marked.</t>
+          <t>Mark x if approved but missing structured regulatory rows. Surfaced in the data-quality panel.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="23.75" customHeight="1" s="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>conventional_approval_only</t>
+          <t>curator_notes</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>set when stage is Approved, no interval is marked, and the only route is oral (an approved conventional drug shown as an API in LA development).</t>
+          <t>Free text for you. Not shown on the dashboard.</t>
         </is>
       </c>
     </row>
@@ -5317,45 +5324,91 @@
       <c r="B28" s="12" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="27">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>RULES THE BUILD STEP CHECKS</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n"/>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>AUTOMATIC FLAGS</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>The build step computes these; you do not enter them:</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="27">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>every row needs</t>
+          <t>missing_frequency</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>a band, a name, an indication and a stage. Missing any of these stops the build with a clear message.</t>
+          <t>set when no interval x is marked.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="27">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>conventional_approval_only</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>set when stage is Approved, no interval is marked, and the only route is oral (an approved conventional drug shown as an API in LA development).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>RULES THE BUILD STEP CHECKS</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>every row needs</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>a band, a name, an indication and a stage. Missing any of these stops the build with a clear message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
           <t>controlled values</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>band, stage, indication and interval codes must match the lists above. Typos are reported by row.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" s="27">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="40" ht="16" customHeight="1" s="27"/>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Dosing timeline,Agents by phase,Class and phase,Counts"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/hiv_curation.xlsx
+++ b/hiv_curation.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20660" yWindow="1900" windowWidth="29080" windowHeight="21800" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1560" yWindow="1760" windowWidth="29080" windowHeight="21800" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Entries" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -141,12 +141,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <sz val="8"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
@@ -160,11 +154,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF12161C"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF12161C"/>
       <sz val="10"/>
     </font>
@@ -395,6 +393,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -405,15 +412,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,52 +672,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AF49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" style="27" min="1" max="1"/>
-    <col width="13" customWidth="1" style="27" min="2" max="2"/>
-    <col width="55.83203125" customWidth="1" style="27" min="3" max="3"/>
-    <col width="12" customWidth="1" style="27" min="4" max="6"/>
-    <col width="30" customWidth="1" style="27" min="7" max="7"/>
-    <col width="21.1640625" customWidth="1" style="27" min="8" max="8"/>
-    <col width="13.33203125" customWidth="1" style="27" min="9" max="10"/>
-    <col width="5" customWidth="1" style="27" min="11" max="11"/>
-    <col width="8" customWidth="1" style="27" min="12" max="12"/>
-    <col width="5" customWidth="1" style="27" min="13" max="16"/>
-    <col width="7.6640625" customWidth="1" style="27" min="17" max="17"/>
-    <col width="8.5" customWidth="1" style="27" min="18" max="18"/>
-    <col width="9" customWidth="1" style="27" min="19" max="21"/>
-    <col width="7.33203125" customWidth="1" style="27" min="22" max="22"/>
-    <col width="17" customWidth="1" style="27" min="23" max="23"/>
-    <col width="9" customWidth="1" style="27" min="24" max="24"/>
-    <col width="10" customWidth="1" style="27" min="25" max="25"/>
-    <col width="11.33203125" customWidth="1" style="27" min="26" max="26"/>
-    <col width="9" customWidth="1" style="27" min="27" max="27"/>
-    <col width="34" customWidth="1" style="27" min="28" max="28"/>
-    <col width="17.1640625" customWidth="1" style="27" min="29" max="29"/>
-    <col width="22.33203125" customWidth="1" style="27" min="30" max="30"/>
-    <col width="26" customWidth="1" style="27" min="31" max="31"/>
+    <col width="6" customWidth="1" style="34" min="1" max="1"/>
+    <col width="13" customWidth="1" style="34" min="2" max="2"/>
+    <col width="55.83203125" customWidth="1" style="34" min="3" max="3"/>
+    <col width="12" customWidth="1" style="34" min="4" max="6"/>
+    <col width="30" customWidth="1" style="34" min="7" max="7"/>
+    <col width="21.1640625" customWidth="1" style="34" min="8" max="8"/>
+    <col width="13.33203125" customWidth="1" style="34" min="9" max="10"/>
+    <col width="5" customWidth="1" style="34" min="11" max="11"/>
+    <col width="8" customWidth="1" style="34" min="12" max="12"/>
+    <col width="5" customWidth="1" style="34" min="13" max="16"/>
+    <col width="7.6640625" customWidth="1" style="34" min="17" max="17"/>
+    <col width="8.5" customWidth="1" style="34" min="18" max="18"/>
+    <col width="9" customWidth="1" style="34" min="19" max="21"/>
+    <col width="7.33203125" customWidth="1" style="34" min="22" max="22"/>
+    <col width="17" customWidth="1" style="34" min="23" max="23"/>
+    <col width="9" customWidth="1" style="34" min="24" max="24"/>
+    <col width="10" customWidth="1" style="34" min="25" max="25"/>
+    <col width="11.33203125" customWidth="1" style="34" min="26" max="26"/>
+    <col width="9" customWidth="1" style="34" min="27" max="27"/>
+    <col width="34" customWidth="1" style="34" min="28" max="28"/>
+    <col width="17.1640625" customWidth="1" style="34" min="29" max="29"/>
+    <col width="22.33203125" customWidth="1" style="34" min="30" max="30"/>
+    <col width="26" customWidth="1" style="34" min="31" max="31"/>
+    <col width="14" customWidth="1" style="34" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="27">
-      <c r="I1" s="28" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="34">
+      <c r="I1" s="35" t="inlineStr">
         <is>
           <t>ROUTE  (mark x)</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="36" t="inlineStr">
         <is>
           <t>DOSING INTERVAL  (mark x)</t>
         </is>
       </c>
-      <c r="AA1" s="26" t="inlineStr">
+      <c r="AA1" s="33" t="inlineStr">
         <is>
           <t>EXCLUDE FROM DASHBOARD</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="33.75" customHeight="1" s="27">
+    <row r="2" ht="33.75" customHeight="1" s="34">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -875,8 +874,13 @@
           <t>class_group</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="27">
+      <c r="AF2" s="24" t="inlineStr">
+        <is>
+          <t>on_hold_discontinued</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="34">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>f001</t>
@@ -965,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="27">
+    <row r="4" ht="15" customHeight="1" s="34">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>f002</t>
@@ -1058,7 +1062,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="27">
+    <row r="5" ht="15" customHeight="1" s="34">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>f003</t>
@@ -1151,7 +1155,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="27">
+    <row r="6" ht="15" customHeight="1" s="34">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>f004</t>
@@ -1244,7 +1248,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="27">
+    <row r="7" ht="15" customHeight="1" s="34">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>f005</t>
@@ -1313,7 +1317,7 @@
       <c r="V7" s="8" t="n"/>
       <c r="W7" s="5" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>manually confirmed</t>
         </is>
       </c>
       <c r="X7" s="5" t="n"/>
@@ -1333,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="27">
+    <row r="8" ht="15" customHeight="1" s="34">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>f006</t>
@@ -1422,7 +1426,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="27">
+    <row r="9" ht="15" customHeight="1" s="34">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>f007</t>
@@ -1515,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="27">
+    <row r="10" ht="15" customHeight="1" s="34">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>f008</t>
@@ -1608,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="27">
+    <row r="11" ht="15" customHeight="1" s="34">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>f009</t>
@@ -1697,7 +1701,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="27">
+    <row r="12" ht="15" customHeight="1" s="34">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>f010</t>
@@ -1790,7 +1794,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="27">
+    <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>f011</t>
@@ -1887,7 +1891,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="27">
+    <row r="14" ht="15" customHeight="1" s="34">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>f012</t>
@@ -1984,7 +1988,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="27">
+    <row r="15" ht="15" customHeight="1" s="34">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>f013</t>
@@ -2069,7 +2073,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="27">
+    <row r="16" ht="15" customHeight="1" s="34">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>f014</t>
@@ -2154,7 +2158,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="27">
+    <row r="17" ht="15" customHeight="1" s="34">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>f015</t>
@@ -2229,7 +2233,11 @@
       </c>
       <c r="Y17" s="5" t="n"/>
       <c r="Z17" s="5" t="n"/>
-      <c r="AA17" s="18" t="n"/>
+      <c r="AA17" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB17" s="19" t="n"/>
       <c r="AC17" t="inlineStr">
         <is>
@@ -2243,7 +2251,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="27">
+    <row r="18" ht="15" customHeight="1" s="34">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>f016</t>
@@ -2314,7 +2322,11 @@
       </c>
       <c r="Y18" s="5" t="n"/>
       <c r="Z18" s="5" t="n"/>
-      <c r="AA18" s="18" t="n"/>
+      <c r="AA18" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB18" s="19" t="n"/>
       <c r="AC18" t="inlineStr">
         <is>
@@ -2328,7 +2340,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="27">
+    <row r="19" ht="15" customHeight="1" s="34">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>f017</t>
@@ -2413,7 +2425,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="27">
+    <row r="20" ht="15" customHeight="1" s="34">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>f018</t>
@@ -2502,7 +2514,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="27">
+    <row r="21" ht="15" customHeight="1" s="34">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>f019</t>
@@ -2603,7 +2615,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="27">
+    <row r="22" ht="15" customHeight="1" s="34">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>f020</t>
@@ -2688,7 +2700,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="27">
+    <row r="23" ht="15" customHeight="1" s="34">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>f021</t>
@@ -2763,7 +2775,11 @@
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="5" t="n"/>
       <c r="Z23" s="5" t="n"/>
-      <c r="AA23" s="18" t="n"/>
+      <c r="AA23" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB23" s="19" t="n"/>
       <c r="AC23" t="inlineStr">
         <is>
@@ -2777,7 +2793,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="27">
+    <row r="24" ht="15" customHeight="1" s="34">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>f022</t>
@@ -2848,7 +2864,11 @@
       <c r="X24" s="5" t="n"/>
       <c r="Y24" s="5" t="n"/>
       <c r="Z24" s="5" t="n"/>
-      <c r="AA24" s="18" t="n"/>
+      <c r="AA24" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB24" s="19" t="n"/>
       <c r="AC24" t="inlineStr">
         <is>
@@ -2862,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="27">
+    <row r="25" ht="15" customHeight="1" s="34">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>f023</t>
@@ -2951,7 +2971,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="27">
+    <row r="26" ht="15" customHeight="1" s="34">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>f024</t>
@@ -3036,7 +3056,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="27">
+    <row r="27" ht="15" customHeight="1" s="34">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>f025</t>
@@ -3129,7 +3149,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="27">
+    <row r="28" ht="15" customHeight="1" s="34">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>f026</t>
@@ -3218,7 +3238,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="27">
+    <row r="29" ht="15" customHeight="1" s="34">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>f027</t>
@@ -3311,7 +3331,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="27">
+    <row r="30" ht="15" customHeight="1" s="34">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>f028</t>
@@ -3382,11 +3402,7 @@
       <c r="X30" s="5" t="n"/>
       <c r="Y30" s="5" t="n"/>
       <c r="Z30" s="5" t="n"/>
-      <c r="AA30" s="18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="AA30" s="18" t="n"/>
       <c r="AB30" s="19" t="n"/>
       <c r="AC30" t="inlineStr">
         <is>
@@ -3400,7 +3416,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="27">
+    <row r="31" ht="15" customHeight="1" s="34">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>f029</t>
@@ -3489,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="27">
+    <row r="32" ht="15" customHeight="1" s="34">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>c030</t>
@@ -3574,7 +3590,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="27">
+    <row r="33" ht="15" customHeight="1" s="34">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>c032</t>
@@ -3659,7 +3675,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="27">
+    <row r="34" ht="15" customHeight="1" s="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>c033</t>
@@ -3742,7 +3758,11 @@
       <c r="X34" s="5" t="n"/>
       <c r="Y34" s="5" t="n"/>
       <c r="Z34" s="5" t="n"/>
-      <c r="AA34" s="18" t="n"/>
+      <c r="AA34" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB34" s="19" t="n"/>
       <c r="AC34" t="inlineStr">
         <is>
@@ -3756,7 +3776,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="27">
+    <row r="35" ht="15" customHeight="1" s="34">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>c034</t>
@@ -3831,7 +3851,11 @@
       <c r="X35" s="5" t="n"/>
       <c r="Y35" s="5" t="n"/>
       <c r="Z35" s="5" t="n"/>
-      <c r="AA35" s="18" t="n"/>
+      <c r="AA35" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB35" s="19" t="n"/>
       <c r="AC35" t="inlineStr">
         <is>
@@ -3845,7 +3869,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="27">
+    <row r="36" ht="15" customHeight="1" s="34">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>c035</t>
@@ -3934,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="27">
+    <row r="37" ht="15" customHeight="1" s="34">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>c037</t>
@@ -4017,7 +4041,11 @@
       </c>
       <c r="Y37" s="5" t="n"/>
       <c r="Z37" s="5" t="n"/>
-      <c r="AA37" s="18" t="n"/>
+      <c r="AA37" s="18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB37" s="19" t="n"/>
       <c r="AC37" t="inlineStr">
         <is>
@@ -4031,7 +4059,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="27">
+    <row r="38" ht="15" customHeight="1" s="34">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>c038</t>
@@ -4120,7 +4148,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="27">
+    <row r="39" ht="15" customHeight="1" s="34">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>c039</t>
@@ -4221,7 +4249,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="27">
+    <row r="40" ht="15" customHeight="1" s="34">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>c040</t>
@@ -4314,7 +4342,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="27">
+    <row r="41" ht="15" customHeight="1" s="34">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>c041</t>
@@ -4415,7 +4443,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="27">
+    <row r="42" ht="15" customHeight="1" s="34">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>c042</t>
@@ -4516,7 +4544,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="27">
+    <row r="43" ht="15" customHeight="1" s="34">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>c043</t>
@@ -4605,7 +4633,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="27">
+    <row r="44" ht="15" customHeight="1" s="34">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>c044</t>
@@ -4690,7 +4718,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="27">
+    <row r="45" ht="15" customHeight="1" s="34">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>c045</t>
@@ -4846,7 +4874,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" s="27">
+    <row r="47" ht="16" customHeight="1" s="34">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>f031</t>
@@ -4857,7 +4885,7 @@
           <t>formulations</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">VH-184+VH-499 </t>
         </is>
@@ -4913,7 +4941,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="27">
+    <row r="48" ht="15" customHeight="1" s="34">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>f032</t>
@@ -4954,7 +4982,7 @@
           <t>INSTI + NNRTI</t>
         </is>
       </c>
-      <c r="K48" s="32" t="inlineStr">
+      <c r="K48" s="28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4976,7 +5004,66 @@
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="5" t="n"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>f033</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>formulations</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Dapivirine ring 3-monthly</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Prevention</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Late-stage</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Phase II/III</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Population Council</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>manually confirmed</t>
+        </is>
+      </c>
+      <c r="AE49" s="5" t="inlineStr">
+        <is>
+          <t>NNRTI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:AE2"/>
@@ -4985,12 +5072,12 @@
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="O1:V1"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation sqref="B3:B48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose formulations or compounds" prompt="Choose formulations or compounds" type="list">
+  <dataValidations count="9">
+    <dataValidation sqref="B3:B49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose formulations or compounds" prompt="Choose formulations or compounds" type="list">
       <formula1>"formulations,compounds"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D3:D48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Treatment, Prevention or Both" prompt="Treatment, Prevention or Both" type="list">
+    <dataValidation sqref="D3:D49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Treatment, Prevention or Both" prompt="Treatment, Prevention or Both" type="list">
       <formula1>"Treatment,Prevention,Both"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4998,7 +5085,7 @@
       <formula1>"Approved,Late-stage,Early-stage,Not stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="W3:W48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Where the interval came from" prompt="Where the interval came from" type="list">
+    <dataValidation sqref="W3:W49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Where the interval came from" prompt="Where the interval came from" type="list">
       <formula1>"LAPaL record,derived from trials,manually confirmed,not stated"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5012,9 +5099,12 @@
     <dataValidation sqref="AE3:AE45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a class, or a combination for a multi-class product." prompt="Pick a class, or a combination for a multi-class product." type="list">
       <formula1>"Capsid inhibitor,INSTI,NNRTI,NRTI,NRTTI,mAb,PI,Fusion inhibitor,Capsid inhibitor + INSTI,Capsid inhibitor + NRTTI,Capsid inhibitor + mAb,INSTI + NNRTI,INSTI + NRTI,NRTI + PI,NRTTI + NNRTI"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Highest clinical phase" prompt="Highest clinical phase" type="list">
+    <dataValidation sqref="F3:F49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Highest clinical phase" prompt="Highest clinical phase" type="list">
       <formula1>"Preclinical,Phase I,Phase I/II,Phase II,Phase II/III,Phase III,Phase IV"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="AF3:AF48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"x"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -5034,11 +5124,11 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="27" min="1" max="1"/>
-    <col width="88" customWidth="1" style="27" min="2" max="2"/>
+    <col width="26" customWidth="1" style="34" min="1" max="1"/>
+    <col width="88" customWidth="1" style="34" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.25" customHeight="1" s="27">
+    <row r="1" ht="16.25" customHeight="1" s="34">
       <c r="A1" s="9" t="inlineStr">
         <is>
           <t>LAPaL long-acting HIV</t>
@@ -5050,40 +5140,40 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="27">
-      <c r="A2" s="33" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="34">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>SETTINGS</t>
         </is>
       </c>
-      <c r="B2" s="34" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="27">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="B2" s="30" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="34">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Default view</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
-        <is>
-          <t>Dosing timeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="27">
-      <c r="A4" s="36" t="n"/>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>Agents by phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="34">
+      <c r="A4" s="32" t="n"/>
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Which view opens first when someone loads the dashboard. Pick one from the dropdown; leave blank to keep Dosing timeline. Run build_data.py afterwards, same as any other change.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="27"/>
-    <row r="6" ht="39" customHeight="1" s="27">
+    <row r="5" ht="15" customHeight="1" s="34"/>
+    <row r="6" ht="39" customHeight="1" s="34">
       <c r="A6" s="11" t="n"/>
       <c r="B6" s="12" t="n"/>
     </row>
-    <row r="7" ht="23.75" customHeight="1" s="27">
+    <row r="7" ht="23.75" customHeight="1" s="34">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
@@ -5091,7 +5181,7 @@
       </c>
       <c r="B7" s="14" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="27">
+    <row r="8" ht="15" customHeight="1" s="34">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>1. Edit the Entries tab</t>
@@ -5103,7 +5193,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="27">
+    <row r="9" ht="15" customHeight="1" s="34">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>2. Save the file</t>
@@ -5115,7 +5205,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="27">
+    <row r="10" ht="15" customHeight="1" s="34">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>3. Run the build step</t>
@@ -5127,7 +5217,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="27">
+    <row r="11" ht="15" customHeight="1" s="34">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>4. Refresh the dashboard</t>
@@ -5139,11 +5229,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="27">
+    <row r="12" ht="15" customHeight="1" s="34">
       <c r="A12" s="11" t="n"/>
       <c r="B12" s="12" t="n"/>
     </row>
-    <row r="13" ht="23.75" customHeight="1" s="27">
+    <row r="13" ht="23.75" customHeight="1" s="34">
       <c r="A13" s="13" t="inlineStr">
         <is>
           <t>COLUMNS</t>
@@ -5151,7 +5241,7 @@
       </c>
       <c r="B13" s="14" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="27">
+    <row r="14" ht="15" customHeight="1" s="34">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>id</t>
@@ -5163,7 +5253,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="27">
+    <row r="15" ht="15" customHeight="1" s="34">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>band</t>
@@ -5175,7 +5265,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="27">
+    <row r="16" ht="15" customHeight="1" s="34">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>name</t>
@@ -5187,7 +5277,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="27">
+    <row r="17" ht="15" customHeight="1" s="34">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>indication</t>
@@ -5199,7 +5289,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="23.75" customHeight="1" s="27">
+    <row r="18" ht="23.75" customHeight="1" s="34">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>stage</t>
@@ -5211,7 +5301,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="23.75" customHeight="1" s="27">
+    <row r="19" ht="23.75" customHeight="1" s="34">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>highest_phase</t>
@@ -5223,7 +5313,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="23.75" customHeight="1" s="27">
+    <row r="20" ht="23.75" customHeight="1" s="34">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>developers</t>
@@ -5235,7 +5325,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="27">
+    <row r="21" ht="15" customHeight="1" s="34">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>drug_class</t>
@@ -5247,7 +5337,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="27">
+    <row r="22" ht="15" customHeight="1" s="34">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>ROUTE columns</t>
@@ -5259,7 +5349,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="27">
+    <row r="23" ht="15" customHeight="1" s="34">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>INTERVAL columns</t>
@@ -5271,7 +5361,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="27">
+    <row r="24" ht="15" customHeight="1" s="34">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>frequency_source</t>
@@ -5283,7 +5373,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="27">
+    <row r="25" ht="15" customHeight="1" s="34">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>flag_no_trials</t>
@@ -5295,7 +5385,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="27">
+    <row r="26" ht="15" customHeight="1" s="34">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>flag_no_reg_rows</t>
@@ -5307,7 +5397,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="23.75" customHeight="1" s="27">
+    <row r="27" ht="23.75" customHeight="1" s="34">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>curator_notes</t>
@@ -5319,11 +5409,11 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="27">
+    <row r="28" ht="15" customHeight="1" s="34">
       <c r="A28" s="11" t="n"/>
       <c r="B28" s="12" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="27">
+    <row r="29" ht="15" customHeight="1" s="34">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <t>AUTOMATIC FLAGS</t>
@@ -5335,7 +5425,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="27">
+    <row r="30" ht="15" customHeight="1" s="34">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>missing_frequency</t>
@@ -5347,7 +5437,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="27">
+    <row r="31" ht="15" customHeight="1" s="34">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>conventional_approval_only</t>
@@ -5395,9 +5485,9 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" s="27"/>
-    <row r="44">
-      <c r="A44" s="30" t="inlineStr">
+    <row r="40" ht="16" customHeight="1" s="34"/>
+    <row r="44" ht="16" customHeight="1" s="34">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
         </is>

--- a/hiv_curation.xlsx
+++ b/hiv_curation.xlsx
@@ -5121,7 +5121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="34" min="1" max="1"/>
@@ -5168,335 +5168,358 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="34"/>
+    <row r="5" ht="15" customHeight="1" s="34">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Default agents sort</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>A to Z</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="39" customHeight="1" s="34">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="12" t="n"/>
-    </row>
-    <row r="7" ht="23.75" customHeight="1" s="34">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>The starting sort for the Agents by phase view, matching its own Sort buttons. Leave blank to keep A to Z. Only matters if that view is what Default view opens on, or once someone visits it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23.75" customHeight="1" s="34"/>
+    <row r="8" ht="15" customHeight="1" s="34">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="34">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>HOW IT WORKS</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="34">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>1. Edit the Entries tab</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>One row per product. Change any white cell. Add or delete whole rows freely; order does not matter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="34">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>2. Save the file</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Keep it as .xlsx.</t>
-        </is>
-      </c>
+      <c r="B9" s="14" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="34">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>3. Run the build step</t>
+          <t>1. Edit the Entries tab</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>In a terminal:  python build_data.py hiv_curation.xlsx  → writes hiv_dashboard_data.json, which the dashboard reads.</t>
+          <t>One row per product. Change any white cell. Add or delete whole rows freely; order does not matter.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="34">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>2. Save the file</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Keep it as .xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="34">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>3. Run the build step</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>In a terminal:  python build_data.py hiv_curation.xlsx  → writes hiv_dashboard_data.json, which the dashboard reads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23.75" customHeight="1" s="34">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
           <t>4. Refresh the dashboard</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>The new data appears. The build step prints a check report and refuses to write if something essential is missing.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="34">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="23.75" customHeight="1" s="34">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="34">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="34">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>COLUMNS</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="34">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Leave as is. Leave blank for a new row and the build step assigns one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="34">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>band</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>formulations = a discrete long-acting product. compounds = an underlying molecule in LA development.</t>
-        </is>
-      </c>
+      <c r="B15" s="14" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="34">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Product or molecule name, shown on the dashboard.</t>
+          <t>Leave as is. Leave blank for a new row and the build step assigns one.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="34">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>indication</t>
+          <t>band</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Treatment, Prevention, or Both. Drives which selection the row appears under. "Both" shows it once, tagged for both.</t>
+          <t>formulations = a discrete long-acting product. compounds = an underlying molecule in LA development.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="23.75" customHeight="1" s="34">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Approved / Late-stage / Early-stage / Not stated. Sets the row colour and grouping.</t>
+          <t>Product or molecule name, shown on the dashboard.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="23.75" customHeight="1" s="34">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>highest_phase</t>
+          <t>indication</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Highest clinical phase on record. Optional, shown in the tooltip.</t>
+          <t>Treatment, Prevention, or Both. Drives which selection the row appears under. "Both" shows it once, tagged for both.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="23.75" customHeight="1" s="34">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>developers</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>One or more, separated by a semicolon ( ; ).</t>
+          <t>Approved / Late-stage / Early-stage / Not stated. Sets the row colour and grouping.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="34">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>drug_class</t>
+          <t>highest_phase</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Optional, shown in the tooltip.</t>
+          <t>Highest clinical phase on record. Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="34">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>ROUTE columns</t>
+          <t>developers</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Mark x under every route that applies. PO oral, SC subcutaneous, IM intramuscular, IV intravenous, VR vaginal ring, TD transdermal.</t>
+          <t>One or more, separated by a semicolon ( ; ).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="34">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>INTERVAL columns</t>
+          <t>drug_class</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Mark x under every dosing interval studied. 1W weekly, 2W 2-weekly, 1M monthly, 2M, 3M, 4M, 6M, 12M yearly. Leave all blank if unknown; the row then sits in the "not stated" lane. Do not enter daily or single-dose.</t>
+          <t>Optional, shown in the tooltip.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="34">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>frequency_source</t>
+          <t>ROUTE columns</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>LAPaL record = confirmed. "derived from trials" = filled from a linked trial and shown with a dagger until you confirm. Change to "manually confirmed" once checked.</t>
+          <t>Mark x under every route that applies. PO oral, SC subcutaneous, IM intramuscular, IV intravenous, VR vaginal ring, TD transdermal.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="34">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>flag_no_trials</t>
+          <t>INTERVAL columns</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Mark x if no clinical trials are linked in LAPaL. Surfaced in the data-quality panel.</t>
+          <t>Mark x under every dosing interval studied. 1W weekly, 2W 2-weekly, 1M monthly, 2M, 3M, 4M, 6M, 12M yearly. Leave all blank if unknown; the row then sits in the "not stated" lane. Do not enter daily or single-dose.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="34">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>flag_no_reg_rows</t>
+          <t>frequency_source</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Mark x if approved but missing structured regulatory rows. Surfaced in the data-quality panel.</t>
+          <t>LAPaL record = confirmed. "derived from trials" = filled from a linked trial and shown with a dagger until you confirm. Change to "manually confirmed" once checked.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="23.75" customHeight="1" s="34">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>flag_no_trials</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Mark x if no clinical trials are linked in LAPaL. Surfaced in the data-quality panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="34">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>flag_no_reg_rows</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Mark x if approved but missing structured regulatory rows. Surfaced in the data-quality panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="34">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>curator_notes</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Free text for you. Not shown on the dashboard.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="34">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="34">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="34">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="34">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>AUTOMATIC FLAGS</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>The build step computes these; you do not enter them:</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="34">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>missing_frequency</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>set when no interval x is marked.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="34">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>conventional_approval_only</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>set when stage is Approved, no interval is marked, and the only route is oral (an approved conventional drug shown as an API in LA development).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="12" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>RULES THE BUILD STEP CHECKS</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>every row needs</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>a band, a name, an indication and a stage. Missing any of these stops the build with a clear message.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>controlled values</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>band, stage, indication and interval codes must match the lists above. Typos are reported by row.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1" s="34"/>
-    <row r="44" ht="16" customHeight="1" s="34">
-      <c r="A44" s="26" t="inlineStr">
+    <row r="44" ht="16" customHeight="1" s="34"/>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>Example: to add a product, copy a row, change name, set band/indication/stage, mark x under each route and interval, leave id blank. Then run build_data.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Dosing timeline,Agents by phase,Class and phase,Counts"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"A to Z,Most advanced,Class,Stage,Entry type"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
